--- a/forms/trg/Formulir_TRG_cul-tor.xlsx
+++ b/forms/trg/Formulir_TRG_cul-tor.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Noel Scott</t>
+          <t>Prof. Muhammad Hasyim, M.Si.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>University of Sunshine Coast and Edith Cowan University | Australia</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Semiotic || Language || Linguistic || Tourism || Cultural Studies</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,13 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>signin?client_id=0000-0002-5982-8983</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="n"/>
+          <t>0000-0003-4827-2737</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6003229</t>
+        </is>
+      </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>14033192900</t>
+          <t>58836450600</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,22 +958,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr.Marianna Sigala</t>
+          <t>Noel Scott</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>University of Newcastle | Australia</t>
+          <t>University of Sunshine Coast and Edith Cowan University | Australia</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>College of Human and Social Futures</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,11 +982,15 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8997-2292</t>
+          <t>signin?client_id=0000-0002-5982-8983</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>14033192900</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,22 +1003,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Bertalan Pusztai</t>
+          <t>Dr.Marianna Sigala</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>University of Szeged | Hongaria</t>
+          <t>University of Newcastle | Australia</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Tourism | Ethnography | Intercultural Communication</t>
+          <t>College of Human and Social Futures</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1023,7 +1027,7 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3440-827X</t>
+          <t>0000-0001-8997-2292</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
@@ -1040,29 +1044,33 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Yinika Perston</t>
+          <t>Prof. Dr. Bertalan Pusztai</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Griffith University | Australia</t>
+          <t>University of Szeged | Hongaria</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Archeology</t>
+          <t>Tourism | Ethnography | Intercultural Communication</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-3440-827X</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
@@ -1077,43 +1085,31 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Aqilah Nurul Khaerani Latif</t>
+          <t>Yinika Perston</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Griffith University | Australia</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Tourism Planning || Management || Tourism of Cultural Heritage || Tourism of Marine Conservation</t>
+          <t>Archeology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0009-0007-1396-7535</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>6778776</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>58657361900</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1126,12 +1122,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ahmad Bahar, S.T., M.Si.</t>
+          <t>Aqilah Nurul Khaerani Latif</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Marine Tourism || Ecotourism</t>
+          <t>Tourism Planning || Management || Tourism of Cultural Heritage || Tourism of Marine Conservation</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1150,17 +1146,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5375-9924</t>
+          <t>0009-0007-1396-7535</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>5976538</t>
+          <t>6778776</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57208930216</t>
+          <t>58657361900</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1175,12 +1171,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Wahyuddin, M.Hum.</t>
+          <t>Dr. Ahmad Bahar, S.T., M.Si.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1190,7 +1186,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>French Language || Culture and Tourism Studies</t>
+          <t>Marine Tourism || Ecotourism</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1199,12 +1195,12 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-2021-9205</t>
+          <t>0000-0001-5375-9924</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>6690677</t>
+          <t>5976538</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -1224,31 +1220,43 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Suryatman</t>
+          <t>Dr. Wahyuddin, M.Hum.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Archeology</t>
+          <t>French Language || Culture and Tourism Studies</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0009-0002-2021-9205</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>6690677</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>57208930216</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1261,16 +1269,24 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Syamsul Rijal</t>
+          <t>Suryatman</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Archeology</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1290,12 +1306,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Syahrul Ramadhani</t>
+          <t>Syamsul Rijal</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1317,10 +1333,22 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Syahrul Ramadhani</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>The Cultural Tourism Research Group explores thematic cultural tourism in South Sulawesi and Indonesia, developing sustainable tourism models to enhance planning, management, and promotion while showcasing Indonesia’s rich cultural heritage.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1328,7 +1356,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1517,15 +1549,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
